--- a/data/trans_orig/Q5405-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5405-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar un telefono en 2007</t>
+          <t>Población según si es capaz de usar un telefono en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10572</t>
+          <t>11855</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28015</t>
+          <t>29317</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15917</t>
+          <t>14525</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35120</t>
+          <t>33856</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>24066</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9674</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25692</t>
+          <t>27144</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23856</t>
+          <t>23961</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45071</t>
+          <t>44659</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>342251</t>
+          <t>342344</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>358823</t>
+          <t>358837</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>539282</t>
+          <t>539301</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>563853</t>
+          <t>563987</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>888016</t>
+          <t>888582</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>917365</t>
+          <t>917999</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10330</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>798</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>7797</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>823</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77600</t>
+          <t>76135</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86442</t>
+          <t>86539</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54350</t>
+          <t>55252</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>136812</t>
+          <t>135743</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147569</t>
+          <t>147750</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1758,97 +1758,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41194</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15007</t>
+          <t>15269</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>11881</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29483</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17340</t>
+          <t>17292</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37626</t>
+          <t>39384</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12510</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>28255</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26765</t>
+          <t>28575</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25852</t>
+          <t>26524</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48682</t>
+          <t>50437</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>464527</t>
+          <t>465631</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>484236</t>
+          <t>484742</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>626513</t>
+          <t>626134</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>650828</t>
+          <t>650983</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1099923</t>
+          <t>1099217</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1129310</t>
+          <t>1128971</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar un telefono en 2012</t>
+          <t>Población según si es capaz de usar un telefono en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>10634</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27928</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18269</t>
+          <t>19121</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40435</t>
+          <t>41335</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31588</t>
+          <t>33143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60151</t>
+          <t>58901</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21750</t>
+          <t>21530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46688</t>
+          <t>45625</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31320</t>
+          <t>31476</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57394</t>
+          <t>56123</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58514</t>
+          <t>58621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95744</t>
+          <t>92321</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>348328</t>
+          <t>349469</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>376456</t>
+          <t>377670</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>546677</t>
+          <t>545886</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>578503</t>
+          <t>578460</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>905551</t>
+          <t>908266</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>950939</t>
+          <t>949073</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,48%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,77 +3264,77 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2424</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>8026</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>9,66%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>3870</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>782</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>11094</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>5,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2424</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>8340</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>10,04%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3870</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1098</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>11687</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>10313</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>12695</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>107148</t>
+          <t>106596</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116576</t>
+          <t>116635</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72784</t>
+          <t>72861</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81983</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>184680</t>
+          <t>184313</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197584</t>
+          <t>197382</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -3700,97 +3700,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2222</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2331</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3813,97 +3813,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5753</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>25,86%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5031</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5529</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>22,61%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4900</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24279</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26575</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17215</t>
+          <t>16493</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43921</t>
+          <t>43292</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29804</t>
+          <t>29849</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20113</t>
+          <t>20273</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42747</t>
+          <t>42064</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37430</t>
+          <t>36569</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66418</t>
+          <t>65796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24857</t>
+          <t>24726</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51926</t>
+          <t>51864</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33153</t>
+          <t>33946</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59969</t>
+          <t>59699</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64233</t>
+          <t>63503</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>100966</t>
+          <t>102239</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>485960</t>
+          <t>486521</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>517658</t>
+          <t>517838</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>643513</t>
+          <t>646771</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>679781</t>
+          <t>680406</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1147254</t>
+          <t>1146114</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1192572</t>
+          <t>1192255</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar un telefono en 2016</t>
+          <t>Población según si es capaz de usar un telefono en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15041</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24358</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>14524</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34354</t>
+          <t>35298</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18225</t>
+          <t>17630</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27190</t>
+          <t>28290</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54506</t>
+          <t>54540</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36790</t>
+          <t>37347</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67391</t>
+          <t>66368</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>326253</t>
+          <t>325115</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>341979</t>
+          <t>342111</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>483983</t>
+          <t>484545</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>515601</t>
+          <t>515212</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>817016</t>
+          <t>817388</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>851520</t>
+          <t>851120</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2283</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4220</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>836</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3886</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>185793</t>
+          <t>185922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191738</t>
+          <t>191745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>180916</t>
+          <t>180674</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>369454</t>
+          <t>369799</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>378881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,62 +5903,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4428</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5849</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35801</t>
+          <t>35758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66374</t>
+          <t>65866</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>74834</t>
+          <t>74824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17280</t>
+          <t>18101</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26533</t>
+          <t>26503</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16737</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38058</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20969</t>
+          <t>20891</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30063</t>
+          <t>29459</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56781</t>
+          <t>57009</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40575</t>
+          <t>41422</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72023</t>
+          <t>72234</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>555845</t>
+          <t>554993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>572407</t>
+          <t>572525</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>703194</t>
+          <t>701187</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>733389</t>
+          <t>733297</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1264666</t>
+          <t>1265450</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1300701</t>
+          <t>1301606</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar un telefono en 2023</t>
+          <t>Población según si es capaz de usar un telefono en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15502</t>
+          <t>14541</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28243</t>
+          <t>27625</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18893</t>
+          <t>18786</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33462</t>
+          <t>33737</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14894</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23195</t>
+          <t>23731</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39344</t>
+          <t>38978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30622</t>
+          <t>30938</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49664</t>
+          <t>49519</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>248962</t>
+          <t>248910</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>259970</t>
+          <t>259832</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>439102</t>
+          <t>438440</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>458670</t>
+          <t>458287</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>692736</t>
+          <t>692726</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>715700</t>
+          <t>716235</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,02%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6899</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>332</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7599</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10356</t>
+          <t>10813</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>9839</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15987</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20317</t>
+          <t>20759</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>260338</t>
+          <t>260371</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>269712</t>
+          <t>269576</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>433444</t>
+          <t>432945</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>452014</t>
+          <t>452956</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>700199</t>
+          <t>699554</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>721959</t>
+          <t>721019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -7810,97 +7810,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>380</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101911</t>
+          <t>101258</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67866</t>
+          <t>67924</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>172026</t>
+          <t>171816</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>175935</t>
+          <t>175931</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>11440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11071</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33927</t>
+          <t>33473</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18983</t>
+          <t>20492</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40330</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23711</t>
+          <t>21746</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19959</t>
+          <t>19298</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53127</t>
+          <t>53286</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35926</t>
+          <t>37472</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67575</t>
+          <t>67228</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>617055</t>
+          <t>618008</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>631793</t>
+          <t>632103</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>944523</t>
+          <t>943138</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>993919</t>
+          <t>995296</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1572660</t>
+          <t>1572563</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1617829</t>
+          <t>1616665</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5405-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5405-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>11650</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10592</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29317</t>
+          <t>28226</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14525</t>
+          <t>15076</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33856</t>
+          <t>35502</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9652</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24066</t>
+          <t>25504</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>10150</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27144</t>
+          <t>26878</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23961</t>
+          <t>23272</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44659</t>
+          <t>46712</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>342344</t>
+          <t>341641</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>358837</t>
+          <t>358954</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>539301</t>
+          <t>539071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>563987</t>
+          <t>562671</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>888582</t>
+          <t>889090</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>917999</t>
+          <t>917564</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10163</t>
+          <t>9774</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>794</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7797</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>952</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>10896</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76135</t>
+          <t>77257</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86539</t>
+          <t>86486</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135743</t>
+          <t>135414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147750</t>
+          <t>148029</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15269</t>
+          <t>14412</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11881</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17292</t>
+          <t>17891</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39384</t>
+          <t>39753</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28255</t>
+          <t>28613</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28575</t>
+          <t>27269</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26524</t>
+          <t>26258</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50437</t>
+          <t>50270</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>465631</t>
+          <t>464648</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>484742</t>
+          <t>484327</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>626134</t>
+          <t>627579</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>650983</t>
+          <t>650948</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1099217</t>
+          <t>1099327</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1128971</t>
+          <t>1130302</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10634</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>27755</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19121</t>
+          <t>18487</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41335</t>
+          <t>40574</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33143</t>
+          <t>33462</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58901</t>
+          <t>60597</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>21624</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45625</t>
+          <t>46142</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31476</t>
+          <t>30584</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56123</t>
+          <t>57827</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58621</t>
+          <t>57643</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92321</t>
+          <t>93070</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>349469</t>
+          <t>350250</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>377670</t>
+          <t>376909</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>545886</t>
+          <t>546796</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>578460</t>
+          <t>578784</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>908266</t>
+          <t>905383</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>949073</t>
+          <t>948628</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,44%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11094</t>
+          <t>10386</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10313</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106596</t>
+          <t>106230</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116635</t>
+          <t>116583</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72861</t>
+          <t>73028</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82002</t>
+          <t>81991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>184313</t>
+          <t>185149</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197382</t>
+          <t>197542</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16493</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43292</t>
+          <t>43035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11646</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29849</t>
+          <t>28999</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>21282</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42064</t>
+          <t>44673</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36569</t>
+          <t>35718</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65796</t>
+          <t>64304</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24726</t>
+          <t>25287</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51864</t>
+          <t>52936</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33946</t>
+          <t>32901</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59699</t>
+          <t>60312</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63503</t>
+          <t>64552</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>102239</t>
+          <t>101061</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>486521</t>
+          <t>486612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>517838</t>
+          <t>517510</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>646771</t>
+          <t>646576</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>680406</t>
+          <t>681240</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1146114</t>
+          <t>1145697</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1192255</t>
+          <t>1192270</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15624</t>
+          <t>14845</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7396</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>25232</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14524</t>
+          <t>13443</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35298</t>
+          <t>33060</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17630</t>
+          <t>17611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>27620</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54540</t>
+          <t>53732</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37347</t>
+          <t>35613</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66368</t>
+          <t>64420</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>325115</t>
+          <t>326273</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>342111</t>
+          <t>342159</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>484545</t>
+          <t>484468</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>515212</t>
+          <t>515506</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>817388</t>
+          <t>818538</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>851120</t>
+          <t>852132</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>185922</t>
+          <t>185052</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191745</t>
+          <t>191736</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>180674</t>
+          <t>180965</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>369799</t>
+          <t>370669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>378881</t>
+          <t>378959</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35758</t>
+          <t>35467</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65866</t>
+          <t>65304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>74824</t>
+          <t>74851</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18101</t>
+          <t>16816</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8366</t>
+          <t>8953</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26503</t>
+          <t>26881</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>38322</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7365</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20891</t>
+          <t>20612</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29459</t>
+          <t>29066</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57009</t>
+          <t>56392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41422</t>
+          <t>40647</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72234</t>
+          <t>72129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>554993</t>
+          <t>555844</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>572525</t>
+          <t>572804</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>701187</t>
+          <t>701472</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>733297</t>
+          <t>733408</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1265450</t>
+          <t>1266040</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1301606</t>
+          <t>1302288</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8262</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20892</t>
+          <t>22243</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14541</t>
+          <t>15753</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27625</t>
+          <t>30209</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>26735</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18786</t>
+          <t>20013</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>36187</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14999</t>
+          <t>15592</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30330</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23731</t>
+          <t>24683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38978</t>
+          <t>41499</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>39657</t>
+          <t>42259</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30938</t>
+          <t>34140</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49519</t>
+          <t>53548</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>255391</t>
+          <t>275915</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>248910</t>
+          <t>269694</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>259832</t>
+          <t>280537</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>449511</t>
+          <t>483967</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>438440</t>
+          <t>471533</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>458287</t>
+          <t>494208</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>704901</t>
+          <t>759882</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>692726</t>
+          <t>747085</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>716235</t>
+          <t>770625</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>769976</t>
+          <t>828876</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>769976</t>
+          <t>828876</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>769976</t>
+          <t>828876</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>10264</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9839</t>
+          <t>10096</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20759</t>
+          <t>19719</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>266212</t>
+          <t>296625</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>260371</t>
+          <t>290513</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>269576</t>
+          <t>300185</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>444489</t>
+          <t>265391</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>432945</t>
+          <t>259670</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>452956</t>
+          <t>269623</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>710701</t>
+          <t>562016</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>699554</t>
+          <t>554354</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>721019</t>
+          <t>568102</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>455036</t>
+          <t>276742</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455036</t>
+          <t>276742</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455036</t>
+          <t>276742</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>728293</t>
+          <t>580567</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>728293</t>
+          <t>580567</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>728293</t>
+          <t>580567</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>601</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7928,12 +7928,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -7963,12 +7963,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -8031,27 +8031,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>104369</t>
+          <t>118280</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101258</t>
+          <t>115840</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8066,27 +8066,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>70344</t>
+          <t>81805</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67924</t>
+          <t>79456</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>174713</t>
+          <t>200085</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171816</t>
+          <t>197008</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>175931</t>
+          <t>201341</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23818</t>
+          <t>25510</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>18485</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33473</t>
+          <t>34487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>30573</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>24343</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41308</t>
+          <t>41262</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9762</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21746</t>
+          <t>23228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38933</t>
+          <t>41705</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>33012</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53286</t>
+          <t>51848</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>53692</t>
+          <t>57014</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37472</t>
+          <t>45934</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67228</t>
+          <t>69354</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>625973</t>
+          <t>690820</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>618008</t>
+          <t>682330</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>632103</t>
+          <t>697443</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>964342</t>
+          <t>831164</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>943138</t>
+          <t>817488</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>995296</t>
+          <t>842206</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1590315</t>
+          <t>1521983</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1572563</t>
+          <t>1507774</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1616665</t>
+          <t>1535807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1027093</t>
+          <t>898378</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1027093</t>
+          <t>898378</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1027093</t>
+          <t>898378</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1674580</t>
+          <t>1611179</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1674580</t>
+          <t>1611179</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1674580</t>
+          <t>1611179</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
